--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20232.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -91,13 +91,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CHONKOA</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>EMILIANO GERARDO</t>
   </si>
 </sst>
 </file>
@@ -834,16 +852,19 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>73.53</v>
+      </c>
+      <c r="H7">
+        <v>7.2</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -857,16 +878,19 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="H8">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1052,16 +1076,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G7">
-        <v>82.34999999999999</v>
+        <v>73.53</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1078,16 +1102,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1121,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1129,25 +1153,71 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920393</v>
+        <v>23330051920122</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>23330051920150</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920205</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20232.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -91,28 +91,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
   </si>
   <si>
     <t>EMILIANO GERARDO</t>
@@ -737,16 +719,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -760,16 +745,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>89.73999999999999</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -783,16 +771,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>88.56999999999999</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -806,16 +797,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>87.5</v>
+      </c>
+      <c r="H5">
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -829,16 +823,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>94.73999999999999</v>
+      </c>
+      <c r="H6">
+        <v>7.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -946,16 +943,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -972,16 +969,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>92.31</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -998,16 +995,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>91.43000000000001</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1024,16 +1021,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>83.33</v>
+        <v>87.5</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1050,16 +1047,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G6">
-        <v>81.58</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1121,7 +1118,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1153,70 +1150,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920122</v>
+        <v>22330051920205</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920150</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920205</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20232.xlsx
+++ b/docentes/Rosas Aguilar Claudia Leonor - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -89,15 +89,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
   </si>
 </sst>
 </file>
@@ -943,13 +934,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H2">
         <v>6.9</v>
@@ -969,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>89.73999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1004,7 +995,7 @@
         <v>88.56999999999999</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1021,16 +1012,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>87.5</v>
+        <v>91.67</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1073,16 +1064,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>73.53</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1099,13 +1090,13 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H8">
         <v>8.5</v>
@@ -1118,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1148,29 +1139,6 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920205</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
